--- a/1-LATEX/2-DADOS/3-OUTPUT/universos_discurso_fuzzy.xlsx
+++ b/1-LATEX/2-DADOS/3-OUTPUT/universos_discurso_fuzzy.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -414,7 +414,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Erosão Intergeracional</t>
+          <t>Erosao Intergeracional</t>
         </is>
       </c>
       <c r="C2">
@@ -454,28 +454,28 @@
         </is>
       </c>
       <c r="C3">
-        <v>-0.06699133405655323</v>
+        <v>-0.08578097560573668</v>
       </c>
       <c r="D3">
-        <v>0.1567300713684782</v>
+        <v>0.1188828612621414</v>
       </c>
       <c r="E3">
-        <v>-6.5</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="F3">
-        <v>17</v>
+        <v>12.6</v>
       </c>
       <c r="G3">
-        <v>-0.2573821296825256</v>
+        <v>-0.300246458848912</v>
       </c>
       <c r="H3">
-        <v>0.3471208669944505</v>
+        <v>0.3333483445053167</v>
       </c>
       <c r="I3">
-        <v>-22.7</v>
+        <v>-25.9</v>
       </c>
       <c r="J3">
-        <v>41.5</v>
+        <v>39.6</v>
       </c>
     </row>
     <row r="4">
@@ -486,32 +486,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Singularidade Territorial</t>
+          <t>Status de Documentacao</t>
         </is>
       </c>
       <c r="C4">
-        <v>-0.08972584688411218</v>
+        <v>-0.2098302317032646</v>
       </c>
       <c r="D4">
-        <v>0.2328783135417356</v>
+        <v>0.2246436112336005</v>
       </c>
       <c r="E4">
-        <v>-8.6</v>
+        <v>-18.9</v>
       </c>
       <c r="F4">
-        <v>26.2</v>
+        <v>25.2</v>
       </c>
       <c r="G4">
-        <v>-0.2849219258300118</v>
+        <v>-0.621592444058011</v>
       </c>
       <c r="H4">
-        <v>0.4280743924876352</v>
+        <v>0.6364058235883467</v>
       </c>
       <c r="I4">
-        <v>-24.8</v>
+        <v>-46.3</v>
       </c>
       <c r="J4">
-        <v>53.4</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5">
@@ -522,32 +522,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Status de Documentação</t>
+          <t>Vulnerabilidade Juridica</t>
         </is>
       </c>
       <c r="C5">
-        <v>-0.2098302317032646</v>
+        <v>-0.494023149580271</v>
       </c>
       <c r="D5">
-        <v>0.2246436112336005</v>
+        <v>-0.06343641739196074</v>
       </c>
       <c r="E5">
-        <v>-18.9</v>
+        <v>-39</v>
       </c>
       <c r="F5">
-        <v>25.2</v>
+        <v>-6.1</v>
       </c>
       <c r="G5">
-        <v>-0.621592444058011</v>
+        <v>-1.113866715737241</v>
       </c>
       <c r="H5">
-        <v>0.6364058235883467</v>
+        <v>0.5564071487650096</v>
       </c>
       <c r="I5">
-        <v>-46.3</v>
+        <v>-67.2</v>
       </c>
       <c r="J5">
-        <v>89</v>
+        <v>74.40000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -558,32 +558,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Vulnerabilidade Jurídica</t>
+          <t>Organizacao Social</t>
         </is>
       </c>
       <c r="C6">
-        <v>-0.494023149580271</v>
+        <v>-0.05482597277927126</v>
       </c>
       <c r="D6">
-        <v>-0.06343641739196074</v>
+        <v>0.398026076072213</v>
       </c>
       <c r="E6">
-        <v>-39</v>
+        <v>-5.3</v>
       </c>
       <c r="F6">
-        <v>-6.1</v>
+        <v>48.9</v>
       </c>
       <c r="G6">
-        <v>-1.113866715737241</v>
+        <v>-0.4852238459279455</v>
       </c>
       <c r="H6">
-        <v>0.5564071487650096</v>
+        <v>0.8284239492208872</v>
       </c>
       <c r="I6">
-        <v>-67.2</v>
+        <v>-38.4</v>
       </c>
       <c r="J6">
-        <v>74.40000000000001</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7">
@@ -594,32 +594,104 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Organização Social</t>
+          <t>Vitalidade Linguistica</t>
         </is>
       </c>
       <c r="C7">
-        <v>-0.05482597277927126</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>0.398026076072213</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>-5.3</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>48.9</v>
+        <v>0</v>
       </c>
       <c r="G7">
-        <v>-0.4852238459279455</v>
+        <v>-0.7100502051691578</v>
       </c>
       <c r="H7">
-        <v>0.8284239492208872</v>
+        <v>0.7100502051691578</v>
       </c>
       <c r="I7">
-        <v>-38.4</v>
+        <v>-50.8</v>
       </c>
       <c r="J7">
-        <v>129</v>
+        <v>103.4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>V7</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Integracao ao Mercado</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>-0.008771158994193784</v>
+      </c>
+      <c r="D8">
+        <v>0.111186312833623</v>
+      </c>
+      <c r="E8">
+        <v>-0.9</v>
+      </c>
+      <c r="F8">
+        <v>11.8</v>
+      </c>
+      <c r="G8">
+        <v>-0.5596308859052627</v>
+      </c>
+      <c r="H8">
+        <v>0.6620460397446918</v>
+      </c>
+      <c r="I8">
+        <v>-42.9</v>
+      </c>
+      <c r="J8">
+        <v>93.90000000000001</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>V8</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Exposicao Climatica</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>0.03385813407672725</v>
+      </c>
+      <c r="D9">
+        <v>0.5254936913432123</v>
+      </c>
+      <c r="E9">
+        <v>3.4</v>
+      </c>
+      <c r="F9">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="G9">
+        <v>0.04126572789340124</v>
+      </c>
+      <c r="H9">
+        <v>0.5180860975265383</v>
+      </c>
+      <c r="I9">
+        <v>4.2</v>
+      </c>
+      <c r="J9">
+        <v>67.90000000000001</v>
       </c>
     </row>
   </sheetData>
